--- a/exports/TATACONSUM_full_report.xlsx
+++ b/exports/TATACONSUM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.57</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>725.95</v>
+        <v>708.75</v>
       </c>
       <c r="I2" t="n">
         <v>719.9540243853542</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.44</v>
+        <v>-2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.97</v>
+        <v>3.26</v>
       </c>
       <c r="M2" t="n">
         <v>0.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>691.3</v>
+        <v>712</v>
       </c>
       <c r="I3" t="n">
         <v>702.7439281480279</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>2.46</v>
+        <v>-0.46</v>
       </c>
       <c r="L3" t="n">
         <v>7.17</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.48</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>809.6</v>
+        <v>779.3</v>
       </c>
       <c r="I4" t="n">
         <v>781.923348151991</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>13.71</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>2.12</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.45</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>740.3</v>
+        <v>764.5</v>
       </c>
       <c r="I5" t="n">
         <v>747.0497198206461</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="L5" t="n">
         <v>5.84</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.33</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>727.55</v>
+        <v>713.65</v>
       </c>
       <c r="I6" t="n">
         <v>716.4155165854606</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.83</v>
+        <v>-6.65</v>
       </c>
       <c r="L6" t="n">
-        <v>6.15</v>
+        <v>6.84</v>
       </c>
       <c r="M6" t="n">
         <v>1.81</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>718.35</v>
+        <v>735.75</v>
       </c>
       <c r="I7" t="n">
         <v>735.7364684037648</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.66</v>
+        <v>-3.1</v>
       </c>
       <c r="L7" t="n">
         <v>3.63</v>
@@ -840,7 +923,7 @@
         <v>1.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="O7" t="n">
         <v>-1.73</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.03</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44783.55208333334</v>
+        <v>44784.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>780.3</v>
+        <v>768.65</v>
       </c>
       <c r="I8" t="n">
         <v>774.7164401873058</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>6.06</v>
+        <v>4.47</v>
       </c>
       <c r="L8" t="n">
         <v>3.17</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.44</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44790.38541666666</v>
+        <v>44790.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>774.3</v>
+        <v>785.25</v>
       </c>
       <c r="I9" t="n">
         <v>784.5274344617853</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.74</v>
+        <v>-2.16</v>
       </c>
       <c r="L9" t="n">
         <v>2.61</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.7</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>826.65</v>
+        <v>790.35</v>
       </c>
       <c r="I10" t="n">
         <v>801.3351025914392</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>5.27</v>
+        <v>0.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.87</v>
@@ -1011,7 +1130,7 @@
         <v>1.43</v>
       </c>
       <c r="N10" t="n">
-        <v>2.63</v>
+        <v>4.68</v>
       </c>
       <c r="O10" t="n">
         <v>2.07</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.19</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>760.55</v>
+        <v>777.25</v>
       </c>
       <c r="I11" t="n">
         <v>773.25101066343</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K11" t="n">
-        <v>3.77</v>
+        <v>1.66</v>
       </c>
       <c r="L11" t="n">
         <v>4.94</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.8</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>787.35</v>
+        <v>773.8</v>
       </c>
       <c r="I12" t="n">
         <v>780.3555147342722</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3</v>
+        <v>-0.44</v>
       </c>
       <c r="L12" t="n">
         <v>3.13</v>
@@ -1125,7 +1268,7 @@
         <v>0.52</v>
       </c>
       <c r="N12" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="O12" t="n">
         <v>1.88</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>702.25</v>
+        <v>705.55</v>
       </c>
       <c r="I13" t="n">
         <v>703.3482918848996</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>101</v>
       </c>
       <c r="K13" t="n">
-        <v>9.25</v>
+        <v>8.82</v>
       </c>
       <c r="L13" t="n">
         <v>1.82</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>3.28</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45034.38541666666</v>
+        <v>45034.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>701.95</v>
+        <v>698.75</v>
       </c>
       <c r="I14" t="n">
         <v>699.0146875046568</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="M14" t="n">
         <v>0.42</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>2.7</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>692.3</v>
+        <v>719.45</v>
       </c>
       <c r="I15" t="n">
         <v>707.366309268193</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.92</v>
+        <v>-2.96</v>
       </c>
       <c r="L15" t="n">
-        <v>0.54</v>
+        <v>3.15</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="N15" t="n">
-        <v>0.28</v>
+        <v>4.82</v>
       </c>
       <c r="O15" t="n">
         <v>-0.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>766.9</v>
+        <v>753.15</v>
       </c>
       <c r="I16" t="n">
         <v>760.6363395617544</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>6.6</v>
+        <v>4.68</v>
       </c>
       <c r="L16" t="n">
         <v>3.07</v>
@@ -1353,7 +1544,7 @@
         <v>0.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
         <v>4.82</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>3.56</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45071.55208333334</v>
+        <v>45072.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>770.5</v>
+        <v>778.35</v>
       </c>
       <c r="I17" t="n">
         <v>777.896963804795</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.3</v>
+        <v>-3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
         <v>-1.38</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.28</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>823.75</v>
+        <v>817.7</v>
       </c>
       <c r="I18" t="n">
         <v>819.2550727268215</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K18" t="n">
-        <v>5.83</v>
+        <v>5.06</v>
       </c>
       <c r="L18" t="n">
         <v>0.87</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45125.38541666666</v>
+        <v>45125.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>846.95</v>
+        <v>848.45</v>
       </c>
       <c r="I19" t="n">
         <v>847.1402569831732</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.58</v>
+        <v>-3.76</v>
       </c>
       <c r="L19" t="n">
-        <v>3.97</v>
+        <v>4.24</v>
       </c>
       <c r="M19" t="n">
         <v>0.9</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>3.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>846.5</v>
+        <v>832.45</v>
       </c>
       <c r="I20" t="n">
         <v>833.3116351703928</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.23</v>
+        <v>-1.89</v>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="N20" t="n">
         <v>2.6</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.39</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>837.6</v>
+        <v>871.1</v>
       </c>
       <c r="I21" t="n">
         <v>845.9314620733082</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.62</v>
+        <v>-4.64</v>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>4.77</v>
       </c>
       <c r="M21" t="n">
         <v>0.71</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.77</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>863.1</v>
+        <v>848.1</v>
       </c>
       <c r="I22" t="n">
         <v>854.76795897084</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.92</v>
+        <v>-2.64</v>
       </c>
       <c r="L22" t="n">
         <v>4.08</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45211.55208333334</v>
+        <v>45212.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>881.55</v>
+        <v>903.6</v>
       </c>
       <c r="I23" t="n">
         <v>883.7815135914044</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.94</v>
+        <v>-6.54</v>
       </c>
       <c r="L23" t="n">
-        <v>4.49</v>
+        <v>6.92</v>
       </c>
       <c r="M23" t="n">
         <v>0.78</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>2.13</v>
       </c>
       <c r="O23" t="n">
         <v>-1.01</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>880.4</v>
+        <v>870.95</v>
       </c>
       <c r="I24" t="n">
         <v>872.6352875731289</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.57</v>
+        <v>-3.61</v>
       </c>
       <c r="L24" t="n">
         <v>3.91</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.99</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>901.8</v>
+        <v>908.4</v>
       </c>
       <c r="I25" t="n">
         <v>907.3990051461681</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.54</v>
+        <v>-4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="M25" t="n">
         <v>0.74</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.46</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1202.8</v>
+        <v>1171.8</v>
       </c>
       <c r="I26" t="n">
         <v>1180.114435838439</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>127.1666666666667</v>
+        <v>128</v>
       </c>
       <c r="K26" t="n">
-        <v>32.41</v>
+        <v>29</v>
       </c>
       <c r="L26" t="n">
         <v>2.52</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.89</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45392.38541666666</v>
+        <v>45392.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1122.05</v>
+        <v>1124.3</v>
       </c>
       <c r="I27" t="n">
         <v>1123.787198452655</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="L27" t="n">
         <v>2.82</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.73</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1095.4</v>
+        <v>1083.35</v>
       </c>
       <c r="I28" t="n">
         <v>1090.047012164681</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.57</v>
+        <v>-3.64</v>
       </c>
       <c r="L28" t="n">
-        <v>3.01</v>
+        <v>5.35</v>
       </c>
       <c r="M28" t="n">
         <v>5.55</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.28</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45434.38541666666</v>
+        <v>45434.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1100.95</v>
+        <v>1107.65</v>
       </c>
       <c r="I29" t="n">
         <v>1105.651161233118</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.62</v>
+        <v>-2.24</v>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="M29" t="n">
         <v>0.92</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>4.41</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45441.38541666666</v>
+        <v>45441.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1071.6</v>
+        <v>1058.65</v>
       </c>
       <c r="I30" t="n">
         <v>1058.759283165548</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.25</v>
+        <v>-4.42</v>
       </c>
       <c r="L30" t="n">
-        <v>3.69</v>
+        <v>4.76</v>
       </c>
       <c r="M30" t="n">
         <v>0.87</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>4.67</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1073.75</v>
+        <v>1130</v>
       </c>
       <c r="I31" t="n">
         <v>1094.080559079113</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.43</v>
+        <v>-6.74</v>
       </c>
       <c r="L31" t="n">
-        <v>1.94</v>
+        <v>8.23</v>
       </c>
       <c r="M31" t="n">
         <v>2.05</v>
       </c>
       <c r="N31" t="n">
-        <v>1.56</v>
+        <v>4.78</v>
       </c>
       <c r="O31" t="n">
         <v>-2.08</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45516.38541666666</v>
+        <v>45516.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1178.85</v>
+        <v>1172.65</v>
       </c>
       <c r="I32" t="n">
         <v>1174.122532253</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>4.32</v>
+        <v>3.77</v>
       </c>
       <c r="L32" t="n">
         <v>5.85</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>4.67</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45530.38541666666</v>
+        <v>45530.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="I33" t="n">
         <v>1215.839114150561</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.61</v>
+        <v>-4.04</v>
       </c>
       <c r="L33" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="M33" t="n">
         <v>0.91</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>3.82</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1195</v>
+        <v>1165.4</v>
       </c>
       <c r="I34" t="n">
         <v>1179.095980260088</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>36</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.05</v>
+        <v>-4.48</v>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="M34" t="n">
-        <v>0.59</v>
+        <v>0.75</v>
       </c>
       <c r="N34" t="n">
-        <v>2.05</v>
+        <v>3.33</v>
       </c>
       <c r="O34" t="n">
         <v>2.01</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.94</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45621.38541666666</v>
+        <v>45621.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>952.35</v>
+        <v>955.6</v>
       </c>
       <c r="I35" t="n">
         <v>955.0993212842566</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>18.28</v>
+        <v>18</v>
       </c>
       <c r="L35" t="n">
         <v>2.11</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>4.76</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>975</v>
+        <v>933.55</v>
       </c>
       <c r="I36" t="n">
         <v>937.2419337351022</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>2.03</v>
+        <v>-2.31</v>
       </c>
       <c r="L36" t="n">
-        <v>1.81</v>
+        <v>2.41</v>
       </c>
       <c r="M36" t="n">
         <v>0.42</v>
       </c>
       <c r="N36" t="n">
-        <v>1.61</v>
+        <v>4.16</v>
       </c>
       <c r="O36" t="n">
         <v>1.34</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>6.96</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>926.9</v>
+        <v>933.9</v>
       </c>
       <c r="I37" t="n">
         <v>932.4208706873225</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>0.71</v>
+        <v>-0.04</v>
       </c>
       <c r="L37" t="n">
         <v>4.33</v>
       </c>
       <c r="M37" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="N37" t="n">
         <v>1.44</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>3.8</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1009</v>
+        <v>996.2</v>
       </c>
       <c r="I38" t="n">
         <v>998.3011085775474</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>8.039999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="L38" t="n">
         <v>0.85</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45743.38541666666</v>
+        <v>45743.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>970</v>
+        <v>980.4</v>
       </c>
       <c r="I39" t="n">
         <v>979.1606830652554</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K39" t="n">
-        <v>2.63</v>
+        <v>1.59</v>
       </c>
       <c r="L39" t="n">
         <v>1.75</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45805.55208333334</v>
+        <v>45806.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1119.7</v>
+        <v>1104.8</v>
       </c>
       <c r="I40" t="n">
         <v>1110.729626678861</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>14.21</v>
+        <v>12.69</v>
       </c>
       <c r="L40" t="n">
         <v>1.09</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.7</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45828.55208333334</v>
+        <v>45831.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1090.9</v>
+        <v>1106.6</v>
       </c>
       <c r="I41" t="n">
         <v>1099.800605611291</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>1.26</v>
+        <v>-0.16</v>
       </c>
       <c r="L41" t="n">
         <v>2.15</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>4.48</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1121</v>
+        <v>1095.1</v>
       </c>
       <c r="I42" t="n">
         <v>1097.036057688218</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>1.3</v>
+        <v>-1.04</v>
       </c>
       <c r="L42" t="n">
         <v>1.5</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.92</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45888.38541666666</v>
+        <v>45888.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1083.3</v>
+        <v>1091.4</v>
       </c>
       <c r="I43" t="n">
         <v>1087.070398343078</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>1.08</v>
+        <v>0.34</v>
       </c>
       <c r="L43" t="n">
         <v>2.89</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>4.43</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1161</v>
+        <v>1136.1</v>
       </c>
       <c r="I44" t="n">
         <v>1138.746158559767</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>105</v>
+        <v>105.8333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>6.38</v>
+        <v>4.1</v>
       </c>
       <c r="L44" t="n">
         <v>3.32</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>5.34</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46007.55208333334</v>
+        <v>46008.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1171.3</v>
+        <v>1182.4</v>
       </c>
       <c r="I45" t="n">
         <v>1182.3956576091</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.1</v>
+        <v>-4.08</v>
       </c>
       <c r="L45" t="n">
-        <v>3.57</v>
+        <v>4.56</v>
       </c>
       <c r="M45" t="n">
         <v>1.71</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.13</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46036.38541666666</v>
+        <v>46036.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="I46" t="n">
         <v>1170.90518334639</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.71</v>
+        <v>-1.13</v>
       </c>
       <c r="L46" t="n">
         <v>1.47</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.84</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46120.55208333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="I47" t="n">
         <v>1074.5785635756</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>84</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>8.550000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="L47" t="n">
         <v>2.99</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.99</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1192</v>
+        <v>1184.2</v>
       </c>
       <c r="I48" t="n">
         <v>1186.814649916776</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K48" t="n">
-        <v>10.68</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L48" t="n">
         <v>1.57</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>981.9</v>
+        <v>995.5</v>
       </c>
       <c r="I49" t="n">
         <v>983.0133480652094</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>142.1666666666667</v>
+        <v>143</v>
       </c>
       <c r="K49" t="n">
-        <v>17.08</v>
+        <v>15.93</v>
       </c>
       <c r="L49" t="n">
         <v>2.26</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>198</v>
+        <v>199</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>3.75</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>970</v>
+        <v>957.45</v>
       </c>
       <c r="I50" t="n">
         <v>958.1389584657736</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.56</v>
+        <v>-3.82</v>
       </c>
       <c r="L50" t="n">
-        <v>3.48</v>
+        <v>4.64</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01</v>
+        <v>0.87</v>
       </c>
       <c r="N50" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="O50" t="n">
         <v>0.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>3.87</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>936.8</v>
+        <v>985.15</v>
       </c>
       <c r="I51" t="n">
         <v>976.3395890055015</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>2.16</v>
+        <v>-2.89</v>
       </c>
       <c r="L51" t="n">
-        <v>1.16</v>
+        <v>4.39</v>
       </c>
       <c r="M51" t="n">
-        <v>0.27</v>
+        <v>3.44</v>
       </c>
       <c r="N51" t="n">
-        <v>0.26</v>
+        <v>5.51</v>
       </c>
       <c r="O51" t="n">
         <v>-1.55</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3408,6 +4031,12 @@
       <c r="Q52" t="n">
         <v>2</v>
       </c>
+      <c r="R52" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5510,7 +6139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -5520,7 +6149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="7">
@@ -5530,7 +6159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.2</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -5540,7 +6169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -5550,7 +6179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42.9</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +6189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="11">
@@ -5600,7 +6229,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="15">
@@ -5610,7 +6239,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="16">
@@ -5620,7 +6249,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.09</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="17">
@@ -5630,7 +6259,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -5640,7 +6269,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -5650,7 +6279,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.92</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="20">
@@ -5660,7 +6289,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.72</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="21">
@@ -5670,7 +6299,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.17</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="22">
@@ -5680,7 +6309,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -5700,7 +6329,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="25">
@@ -5720,7 +6349,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.41</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="27">
@@ -5730,7 +6359,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.29</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="28">
@@ -5740,7 +6369,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
